--- a/tally_templates/DXQD.xlsx
+++ b/tally_templates/DXQD.xlsx
@@ -1489,7 +1489,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="10">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * -_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-412]yyyy-mm-dd"/>
@@ -2568,7 +2568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="419">
+  <cellXfs count="433">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
@@ -3824,6 +3824,48 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3831,11 +3873,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4041,7 +4083,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF333300"/>
   </sheetPr>
@@ -4339,7 +4381,7 @@
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="419" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="7"/>
@@ -4354,7 +4396,7 @@
       <c r="J4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="K4" s="420"/>
       <c r="L4" s="9">
         <v>46231</v>
       </c>
@@ -4375,7 +4417,7 @@
       <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="421" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="8"/>
@@ -4384,13 +4426,13 @@
       <c r="F6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="422"/>
       <c r="H6" s="12"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="K6" s="420"/>
       <c r="L6" s="13" t="s">
         <v>10</v>
       </c>
@@ -12077,7 +12119,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IW115"/>
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.9921875" customHeight="1"/>
   <cols>
@@ -12294,7 +12336,7 @@
       <c r="A6" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="B6" s="37"/>
+      <c r="B6" s="428"/>
       <c r="C6" s="37"/>
       <c r="D6" s="195" t="str">
         <f>'Final Work'!B4</f>
@@ -12825,7 +12867,7 @@
       <c r="A8" s="100" t="s">
         <v>176</v>
       </c>
-      <c r="B8" s="100"/>
+      <c r="B8" s="432"/>
       <c r="C8" s="100"/>
       <c r="D8" s="195" t="s">
         <v>7</v>
@@ -12843,7 +12885,7 @@
       <c r="O8" s="210" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="100"/>
+      <c r="P8" s="432"/>
       <c r="Q8" s="100"/>
       <c r="R8" s="109">
         <v>15</v>
@@ -12859,7 +12901,7 @@
       </c>
       <c r="Z8" s="211"/>
       <c r="AA8" s="211"/>
-      <c r="AB8" s="37" t="s">
+      <c r="AB8" s="428" t="s">
         <v>32</v>
       </c>
       <c r="AC8" s="37"/>
@@ -40758,7 +40800,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IW43"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.9921875" customHeight="1"/>
   <cols>
@@ -41358,21 +41400,21 @@
       <c r="A8" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="105" t="s">
+      <c r="B8" s="423" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="108"/>
       <c r="D8" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="423">
         <v>15</v>
       </c>
       <c r="F8" s="105"/>
       <c r="G8" s="109" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="110" t="s">
+      <c r="H8" s="424" t="s">
         <v>39</v>
       </c>
       <c r="I8" s="104"/>
@@ -43518,7 +43560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF333300"/>
   </sheetPr>
@@ -43844,14 +43886,14 @@
       <c r="G6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="136" t="s">
+      <c r="H6" s="143" t="s">
         <v>48</v>
       </c>
       <c r="I6" s="136"/>
       <c r="K6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="142">
+      <c r="L6" s="425">
         <v>46230</v>
       </c>
       <c r="M6" s="142"/>
@@ -44351,7 +44393,7 @@
       <c r="A8" s="141" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="426" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="144"/>
@@ -44359,14 +44401,14 @@
       <c r="G8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="136" t="s">
+      <c r="H8" s="143" t="s">
         <v>7</v>
       </c>
       <c r="I8" s="136"/>
       <c r="K8" s="141" t="s">
         <v>52</v>
       </c>
-      <c r="L8" s="136">
+      <c r="L8" s="143">
         <v>15</v>
       </c>
       <c r="M8" s="136"/>
@@ -47415,7 +47457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF333300"/>
   </sheetPr>
@@ -47771,7 +47813,7 @@
       <c r="A8" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="141" t="s">
+      <c r="B8" s="143" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="141"/>
@@ -47780,7 +47822,7 @@
       <c r="I8" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="136"/>
+      <c r="J8" s="143"/>
       <c r="K8" s="141" t="s">
         <v>7</v>
       </c>
@@ -47796,7 +47838,7 @@
       <c r="R8" s="136"/>
     </row>
     <row r="9" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" ht="12" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="145" t="s">
         <v>12</v>
       </c>
@@ -47830,7 +47872,7 @@
       <c r="Q10" s="145"/>
       <c r="R10" s="145"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="145"/>
       <c r="B11" s="145"/>
       <c r="C11" s="145"/>
@@ -47853,32 +47895,18 @@
       <c r="R11" s="145"/>
     </row>
     <row r="12" ht="22.9" customHeight="1" spans="1:257" x14ac:dyDescent="0.25">
-      <c r="A12" s="178" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="178" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="179" t="s">
-        <v>79</v>
-      </c>
+      <c r="A12" s="178"/>
+      <c r="B12" s="178"/>
+      <c r="C12" s="179"/>
       <c r="D12" s="179"/>
       <c r="E12" s="179"/>
-      <c r="F12" s="179" t="s">
-        <v>80</v>
-      </c>
+      <c r="F12" s="179"/>
       <c r="G12" s="179"/>
       <c r="H12" s="179"/>
       <c r="I12" s="179"/>
-      <c r="J12" s="179">
-        <v>1</v>
-      </c>
-      <c r="K12" s="179" t="s">
-        <v>64</v>
-      </c>
-      <c r="L12" s="180" t="s">
-        <v>81</v>
-      </c>
+      <c r="J12" s="179"/>
+      <c r="K12" s="179"/>
+      <c r="L12" s="180"/>
       <c r="M12" s="180"/>
       <c r="N12" s="180"/>
       <c r="O12" s="180"/>
@@ -51597,7 +51625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF333300"/>
   </sheetPr>
@@ -51923,7 +51951,7 @@
       <c r="G6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="136" t="s">
+      <c r="H6" s="143" t="s">
         <v>83</v>
       </c>
       <c r="I6" s="136"/>
@@ -51945,7 +51973,7 @@
       <c r="A8" s="141" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="426" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="144"/>
@@ -51953,14 +51981,14 @@
       <c r="G8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="136" t="s">
+      <c r="H8" s="143" t="s">
         <v>7</v>
       </c>
       <c r="I8" s="136"/>
       <c r="K8" s="141" t="s">
         <v>52</v>
       </c>
-      <c r="L8" s="136">
+      <c r="L8" s="143">
         <v>15</v>
       </c>
       <c r="M8" s="136"/>
@@ -54267,7 +54295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF333300"/>
   </sheetPr>
@@ -54623,7 +54651,7 @@
       <c r="A8" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="141" t="s">
+      <c r="B8" s="143" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="141"/>
@@ -54632,7 +54660,7 @@
       <c r="I8" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="136"/>
+      <c r="J8" s="143"/>
       <c r="K8" s="141" t="s">
         <v>7</v>
       </c>
@@ -54648,7 +54676,7 @@
       <c r="R8" s="136"/>
     </row>
     <row r="9" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" ht="12" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="145" t="s">
         <v>12</v>
       </c>
@@ -54682,7 +54710,7 @@
       <c r="Q10" s="145"/>
       <c r="R10" s="145"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="145"/>
       <c r="B11" s="145"/>
       <c r="C11" s="145"/>
@@ -55103,7 +55131,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IW98"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.9921875" customHeight="1"/>
   <cols>
@@ -55195,7 +55223,7 @@
       <c r="J6" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="K6" s="200">
+      <c r="K6" s="427">
         <v>46230</v>
       </c>
       <c r="L6" s="200"/>
@@ -55220,24 +55248,20 @@
       <c r="A8" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="109" t="s">
-        <v>79</v>
-      </c>
+      <c r="B8" s="428"/>
+      <c r="C8" s="109"/>
       <c r="D8" s="109"/>
       <c r="E8" s="109" t="s">
         <v>90</v>
       </c>
       <c r="F8" s="109"/>
       <c r="G8" s="109"/>
-      <c r="H8" s="37" t="s">
-        <v>91</v>
-      </c>
+      <c r="H8" s="428"/>
       <c r="I8" s="37"/>
       <c r="J8" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="K8" s="109" t="s">
+      <c r="K8" s="429" t="s">
         <v>15</v>
       </c>
       <c r="L8" s="109" t="s">
@@ -55495,7 +55519,7 @@
       <c r="A9" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="B9" s="37"/>
+      <c r="B9" s="428"/>
       <c r="C9" s="109" t="s">
         <v>19</v>
       </c>
@@ -56780,7 +56804,7 @@
       </c>
       <c r="B30" s="210"/>
       <c r="C30" s="210"/>
-      <c r="D30" s="211"/>
+      <c r="D30" s="430"/>
       <c r="E30" s="211"/>
       <c r="F30" s="211"/>
       <c r="G30" s="211"/>
@@ -56809,9 +56833,7 @@
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:257" x14ac:dyDescent="0.25">
       <c r="A32" s="213"/>
-      <c r="B32" s="214" t="s">
-        <v>81</v>
-      </c>
+      <c r="B32" s="214"/>
       <c r="C32" s="214"/>
       <c r="D32" s="214"/>
       <c r="E32" s="214"/>
@@ -59591,7 +59613,7 @@
       <c r="A57" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="B57" s="37"/>
+      <c r="B57" s="428"/>
       <c r="C57" s="109"/>
       <c r="D57" s="109"/>
       <c r="E57" s="109" t="s">
@@ -59599,12 +59621,12 @@
       </c>
       <c r="F57" s="109"/>
       <c r="G57" s="109"/>
-      <c r="H57" s="37"/>
+      <c r="H57" s="428"/>
       <c r="I57" s="37"/>
       <c r="J57" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="K57" s="109" t="s">
+      <c r="K57" s="429" t="s">
         <v>15</v>
       </c>
       <c r="L57" s="109" t="s">
@@ -59862,7 +59884,7 @@
       <c r="A58" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="B58" s="37"/>
+      <c r="B58" s="428"/>
       <c r="C58" s="109"/>
       <c r="D58" s="109"/>
       <c r="E58" s="37"/>
@@ -61145,7 +61167,7 @@
       </c>
       <c r="B79" s="210"/>
       <c r="C79" s="210"/>
-      <c r="D79" s="211"/>
+      <c r="D79" s="430"/>
       <c r="E79" s="211"/>
       <c r="F79" s="211"/>
       <c r="G79" s="211"/>
@@ -63926,7 +63948,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P74"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.9921875" customHeight="1"/>
   <cols>
@@ -64008,7 +64030,7 @@
       <c r="E6" s="231" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="234" t="s">
+      <c r="F6" s="431" t="s">
         <v>32</v>
       </c>
     </row>
@@ -64422,7 +64444,7 @@
       <c r="E42" s="231" t="s">
         <v>131</v>
       </c>
-      <c r="F42" s="234" t="s">
+      <c r="F42" s="431" t="s">
         <v>32</v>
       </c>
     </row>
@@ -64772,7 +64794,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IW124"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.7421875" customHeight="1"/>
   <cols>
@@ -65624,7 +65646,7 @@
       <c r="G7" s="233" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="142">
+      <c r="H7" s="425">
         <v>46230</v>
       </c>
       <c r="I7" s="142"/>
@@ -65646,7 +65668,7 @@
       <c r="G8" s="233" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="423" t="s">
         <v>152</v>
       </c>
       <c r="I8" s="21"/>
@@ -66909,7 +66931,7 @@
       <c r="G49" s="233" t="s">
         <v>9</v>
       </c>
-      <c r="H49" s="21" t="s">
+      <c r="H49" s="423" t="s">
         <v>152</v>
       </c>
       <c r="I49" s="21"/>
@@ -66970,21 +66992,13 @@
       <c r="I52" s="276"/>
     </row>
     <row r="53" ht="21" customHeight="1" hidden="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="196" t="s">
-        <v>164</v>
-      </c>
+      <c r="A53" s="196"/>
       <c r="B53" s="253"/>
-      <c r="C53" s="242" t="s">
-        <v>165</v>
-      </c>
+      <c r="C53" s="242"/>
       <c r="D53" s="197"/>
       <c r="E53" s="197"/>
-      <c r="F53" s="307">
-        <v>-18</v>
-      </c>
-      <c r="G53" s="308">
-        <v>-17.8</v>
-      </c>
+      <c r="F53" s="307"/>
+      <c r="G53" s="308"/>
       <c r="H53" s="309" t="s">
         <v>166</v>
       </c>
@@ -68185,14 +68199,14 @@
       <c r="D90" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E90" s="136">
+      <c r="E90" s="143">
         <v>15</v>
       </c>
       <c r="F90" s="136"/>
       <c r="G90" s="233" t="s">
         <v>9</v>
       </c>
-      <c r="H90" s="21" t="s">
+      <c r="H90" s="423" t="s">
         <v>152</v>
       </c>
       <c r="I90" s="21"/>
